--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T20:38:51+00:00</t>
+    <t>2026-07-29T12:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:58:51+00:00</t>
+    <t>2026-08-03T13:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:35:26+00:00</t>
+    <t>2026-08-11T08:10:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:10:28+00:00</t>
+    <t>2026-08-11T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:02+00:00</t>
+    <t>2026-08-28T09:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -604,7 +604,7 @@
     <t>Type d'allergie / hypersensibilité non allergique / intolérance / idiosyncrasie</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-evenement-indesirable-previsible-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-evenement-indesirable-previsible-cisis|20260716085852</t>
   </si>
   <si>
     <t>Observation.code.nullFlavor</t>
@@ -833,7 +833,7 @@
     <t>L'élément &lt;value&gt; sera utilisé pour indiquer qu'il n'y a pas d'allergie/hypersensibilité ou que l'on ne sait pas à partir du jdv-absent-or-unknown-allergy-cisis (1.2.250.1.213.1.1.5.661).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-absent-or-unknown-allergy-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-absent-or-unknown-allergy-cisis|20260716085852</t>
   </si>
   <si>
     <t>Observation.value.nullFlavor</t>
